--- a/public/templates/forms/A-161-PhishingSimulationResults-FORM.xlsx
+++ b/public/templates/forms/A-161-PhishingSimulationResults-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -188,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -249,6 +254,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -626,7 +634,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -776,7 +784,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="29.75" customHeight="1">
+    <row r="24" ht="34.7" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>« Summarize notable findings or exceptions from the entries above. Mirror items that need tracking into the Risk / Finding Register (POA&amp;M). »</t>
@@ -959,7 +967,7 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="34.7" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter’s note (internal, delete before publishing): list any [BRACKETED] field that could not be resolved from project context, and any decision needing confirmation.</t>
@@ -999,7 +1007,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1032,7 +1040,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, findings, sign-off, retention and revision history live on the Log tab.</t>
@@ -1109,10 +1117,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D8" s="25">
+        <v>46082</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -1298,7 +1304,7 @@
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="20" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Medium (6–25, shared county IT)</t>
@@ -1312,7 +1318,7 @@
       <c r="C20" s="21" t="n"/>
       <c r="D20" s="20" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="34.7" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Large (25+, dedicated IT/security)</t>
@@ -1345,6 +1351,6 @@
     <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>